--- a/data/trans_orig/Q23_tabaco_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007 (tasa de respuesta: 86,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126211</t>
+          <t>128022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164734</t>
+          <t>166107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36376</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61375</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171867</t>
+          <t>172019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214976</t>
+          <t>216577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204579</t>
+          <t>203206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243102</t>
+          <t>241291</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117522</t>
+          <t>118085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142521</t>
+          <t>141613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>333234</t>
+          <t>331633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>376343</t>
+          <t>376191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149756</t>
+          <t>149576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192410</t>
+          <t>192403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49465</t>
+          <t>47746</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75725</t>
+          <t>75172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>209117</t>
+          <t>204357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>263389</t>
+          <t>260444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324132</t>
+          <t>324139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366786</t>
+          <t>366966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203089</t>
+          <t>203642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229349</t>
+          <t>231068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>531967</t>
+          <t>534912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>586239</t>
+          <t>590999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107078</t>
+          <t>106666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143667</t>
+          <t>145608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39020</t>
+          <t>38423</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63351</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>152960</t>
+          <t>154934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197743</t>
+          <t>202638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>203844</t>
+          <t>201903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>240433</t>
+          <t>240845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129765</t>
+          <t>131321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154096</t>
+          <t>154693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342884</t>
+          <t>337989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>387667</t>
+          <t>385693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142946</t>
+          <t>146065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184547</t>
+          <t>185527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84224</t>
+          <t>84640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118710</t>
+          <t>118799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241296</t>
+          <t>242129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294367</t>
+          <t>293664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303150</t>
+          <t>302170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>344751</t>
+          <t>341632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228827</t>
+          <t>228738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>263313</t>
+          <t>262897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>540867</t>
+          <t>541570</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593938</t>
+          <t>593105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>568525</t>
+          <t>572225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>647867</t>
+          <t>650850</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>292311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>816937</t>
+          <t>820550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>916984</t>
+          <t>919160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1073197</t>
+          <t>1070214</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1152539</t>
+          <t>1148839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706059</t>
+          <t>706053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>761677</t>
+          <t>763423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1802443</t>
+          <t>1800267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1902490</t>
+          <t>1898877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012 (tasa de respuesta: 94,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>153310</t>
+          <t>154318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>192999</t>
+          <t>195050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>35354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62045</t>
+          <t>62019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198576</t>
+          <t>196289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>246025</t>
+          <t>246641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>247316</t>
+          <t>245265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287005</t>
+          <t>285997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158931</t>
+          <t>158957</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186158</t>
+          <t>185622</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>415265</t>
+          <t>414649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>462714</t>
+          <t>465001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187115</t>
+          <t>187774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>235526</t>
+          <t>236477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88838</t>
+          <t>88398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124521</t>
+          <t>124953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>289429</t>
+          <t>288916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>347200</t>
+          <t>348961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>387555</t>
+          <t>386604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435966</t>
+          <t>435307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>253698</t>
+          <t>253266</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289381</t>
+          <t>289821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>654100</t>
+          <t>652339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711871</t>
+          <t>712384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142933</t>
+          <t>140090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183968</t>
+          <t>186096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75420</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110094</t>
+          <t>109818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>229459</t>
+          <t>229154</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285236</t>
+          <t>283735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270806</t>
+          <t>268678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311841</t>
+          <t>314684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211334</t>
+          <t>211610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>246008</t>
+          <t>245558</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>490966</t>
+          <t>492467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>546743</t>
+          <t>547048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,48%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164214</t>
+          <t>163478</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99062</t>
+          <t>99272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137548</t>
+          <t>137946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>278191</t>
+          <t>274290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>334244</t>
+          <t>334724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317928</t>
+          <t>316945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361959</t>
+          <t>362695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259260</t>
+          <t>258862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>297746</t>
+          <t>297536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>588737</t>
+          <t>588257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>644790</t>
+          <t>648691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>687193</t>
+          <t>689918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>775790</t>
+          <t>780342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>401390</t>
+          <t>402629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1036339</t>
+          <t>1041138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1150041</t>
+          <t>1156243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1268552</t>
+          <t>1264000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1357149</t>
+          <t>1354424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>916041</t>
+          <t>914802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>986340</t>
+          <t>986094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2211732</t>
+          <t>2205530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2325434</t>
+          <t>2320635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138197</t>
+          <t>138385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178067</t>
+          <t>177533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45706</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72243</t>
+          <t>71514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,47 +4677,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>31,85%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>216260</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>193616</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>241212</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>32,18%</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>216260</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>191168</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>240386</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>35,95%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199005</t>
+          <t>199539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238875</t>
+          <t>238687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152278</t>
+          <t>153007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178815</t>
+          <t>179661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,47 +4790,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>68,15%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>80,02%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>385332</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>360380</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>407976</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>64,05%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>59,9%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>67,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>79,64%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>385332</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>361206</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>410424</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>64,05%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>60,04%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176349</t>
+          <t>179353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223161</t>
+          <t>224542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85995</t>
+          <t>87708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121186</t>
+          <t>122807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279181</t>
+          <t>276150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>336105</t>
+          <t>334882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298687</t>
+          <t>297306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345499</t>
+          <t>342495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237083</t>
+          <t>235462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>272274</t>
+          <t>270561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>544011</t>
+          <t>545234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600935</t>
+          <t>603966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113186</t>
+          <t>114634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153315</t>
+          <t>154095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52719</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82156</t>
+          <t>81100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178190</t>
+          <t>176837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>226147</t>
+          <t>226097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274982</t>
+          <t>274202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315111</t>
+          <t>313663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211507</t>
+          <t>212563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240944</t>
+          <t>240492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>495812</t>
+          <t>495862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543769</t>
+          <t>545122</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>127805</t>
+          <t>126893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167897</t>
+          <t>168044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77628</t>
+          <t>78041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112136</t>
+          <t>111330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218334</t>
+          <t>216843</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272391</t>
+          <t>270505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273726</t>
+          <t>273579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313818</t>
+          <t>314730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255912</t>
+          <t>256718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290420</t>
+          <t>290007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>537280</t>
+          <t>539166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>591337</t>
+          <t>592828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>598752</t>
+          <t>598347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>679504</t>
+          <t>681670</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>292931</t>
+          <t>291263</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>355893</t>
+          <t>356031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>903152</t>
+          <t>904954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1014274</t>
+          <t>1013420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1089335</t>
+          <t>1087169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1170087</t>
+          <t>1170492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>888607</t>
+          <t>888469</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>951569</t>
+          <t>953237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1999065</t>
+          <t>1999919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2110187</t>
+          <t>2108385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93805</t>
+          <t>94013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>126655</t>
+          <t>129998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>21973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39275</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>119926</t>
+          <t>121852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159510</t>
+          <t>161168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163286</t>
+          <t>159943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196136</t>
+          <t>195928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129609</t>
+          <t>129170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147303</t>
+          <t>146911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>299315</t>
+          <t>297657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>338899</t>
+          <t>336973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43333</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>205030</t>
+          <t>206751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>45466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68408</t>
+          <t>68823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87032</t>
+          <t>81419</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>251603</t>
+          <t>254213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427913</t>
+          <t>426192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589610</t>
+          <t>590764</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191306</t>
+          <t>190891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>214669</t>
+          <t>214248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>641054</t>
+          <t>638444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>805625</t>
+          <t>811238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>88927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130216</t>
+          <t>129937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50911</t>
+          <t>50784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77527</t>
+          <t>76251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150935</t>
+          <t>148200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198335</t>
+          <t>201225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210076</t>
+          <t>210355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>251192</t>
+          <t>251365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150032</t>
+          <t>151308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176648</t>
+          <t>176775</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>369517</t>
+          <t>366627</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>416917</t>
+          <t>419652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130177</t>
+          <t>129964</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167700</t>
+          <t>169236</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>73284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99871</t>
+          <t>99119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210503</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>258606</t>
+          <t>258860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238743</t>
+          <t>237207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276266</t>
+          <t>276479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>217683</t>
+          <t>218435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245079</t>
+          <t>244270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>465391</t>
+          <t>465137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>513494</t>
+          <t>512279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>298145</t>
+          <t>296898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>583493</t>
+          <t>587979</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>212404</t>
+          <t>210736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259085</t>
+          <t>259962</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>523840</t>
+          <t>509845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>815602</t>
+          <t>811062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1086127</t>
+          <t>1081641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1371475</t>
+          <t>1372722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>714626</t>
+          <t>713749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>761307</t>
+          <t>762975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1827729</t>
+          <t>1832269</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2119491</t>
+          <t>2133486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>128022</t>
+          <t>126667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166107</t>
+          <t>165714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60812</t>
+          <t>60343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>172019</t>
+          <t>171526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216577</t>
+          <t>218387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>203206</t>
+          <t>203599</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241291</t>
+          <t>242646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118085</t>
+          <t>118554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141613</t>
+          <t>141767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>331633</t>
+          <t>329823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>376191</t>
+          <t>376684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149576</t>
+          <t>151434</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192403</t>
+          <t>193935</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47746</t>
+          <t>48666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75172</t>
+          <t>78571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204357</t>
+          <t>207748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260444</t>
+          <t>258960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324139</t>
+          <t>322607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366966</t>
+          <t>365108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203642</t>
+          <t>200243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231068</t>
+          <t>230148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>534912</t>
+          <t>536396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>590999</t>
+          <t>587608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106666</t>
+          <t>109438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145608</t>
+          <t>145005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38423</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61795</t>
+          <t>62542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154934</t>
+          <t>154686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202638</t>
+          <t>198815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>201903</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>240845</t>
+          <t>238073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131321</t>
+          <t>130574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154693</t>
+          <t>154438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337989</t>
+          <t>341812</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>385693</t>
+          <t>385941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146065</t>
+          <t>146702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185527</t>
+          <t>187543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84640</t>
+          <t>86174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118799</t>
+          <t>117773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242129</t>
+          <t>241593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293664</t>
+          <t>294654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302170</t>
+          <t>300154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341632</t>
+          <t>340995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228738</t>
+          <t>229764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>262897</t>
+          <t>261363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541570</t>
+          <t>540580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593105</t>
+          <t>593641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>572225</t>
+          <t>567441</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>650850</t>
+          <t>653171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234941</t>
+          <t>234847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292311</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>820550</t>
+          <t>821881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>919160</t>
+          <t>921289</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1070214</t>
+          <t>1067893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1148839</t>
+          <t>1153623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706053</t>
+          <t>708290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>763423</t>
+          <t>763517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1800267</t>
+          <t>1798138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1898877</t>
+          <t>1897546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154318</t>
+          <t>154913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>195050</t>
+          <t>198345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35354</t>
+          <t>33990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62019</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196289</t>
+          <t>196499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>246641</t>
+          <t>247753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245265</t>
+          <t>241970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285997</t>
+          <t>285402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158957</t>
+          <t>160493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>185622</t>
+          <t>186986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>414649</t>
+          <t>413537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>465001</t>
+          <t>464791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187774</t>
+          <t>186525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>236477</t>
+          <t>235845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88398</t>
+          <t>88582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124953</t>
+          <t>125812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288916</t>
+          <t>288094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>348961</t>
+          <t>351043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386604</t>
+          <t>387236</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435307</t>
+          <t>436556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>253266</t>
+          <t>252407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289821</t>
+          <t>289637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652339</t>
+          <t>650257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712384</t>
+          <t>713206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140090</t>
+          <t>141356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186096</t>
+          <t>186734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75870</t>
+          <t>75570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109818</t>
+          <t>112666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>229154</t>
+          <t>228825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283735</t>
+          <t>284397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268678</t>
+          <t>268040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314684</t>
+          <t>313418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211610</t>
+          <t>208762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245558</t>
+          <t>245858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>492467</t>
+          <t>491805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547048</t>
+          <t>547377</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163478</t>
+          <t>163594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209228</t>
+          <t>208910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99272</t>
+          <t>100623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137946</t>
+          <t>138346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274290</t>
+          <t>276717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>334724</t>
+          <t>334786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>316945</t>
+          <t>317263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362695</t>
+          <t>362579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258862</t>
+          <t>258462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>297536</t>
+          <t>296185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>588257</t>
+          <t>588195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>648691</t>
+          <t>646264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>689918</t>
+          <t>691164</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>780342</t>
+          <t>779873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331478</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>402629</t>
+          <t>400047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1041138</t>
+          <t>1045128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1156243</t>
+          <t>1159739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1264000</t>
+          <t>1264469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1354424</t>
+          <t>1353178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>914802</t>
+          <t>917384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>986094</t>
+          <t>985953</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2205530</t>
+          <t>2202034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2320635</t>
+          <t>2316645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138385</t>
+          <t>140613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177533</t>
+          <t>180378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44860</t>
+          <t>45547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71514</t>
+          <t>70755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193616</t>
+          <t>193849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>241212</t>
+          <t>241804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199539</t>
+          <t>196694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238687</t>
+          <t>236459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153007</t>
+          <t>153766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>179661</t>
+          <t>178974</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>360380</t>
+          <t>359788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>407976</t>
+          <t>407743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179353</t>
+          <t>176516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>224542</t>
+          <t>221964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87708</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122807</t>
+          <t>122685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>276150</t>
+          <t>274642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334882</t>
+          <t>334747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297306</t>
+          <t>299884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342495</t>
+          <t>345332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235462</t>
+          <t>235584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>270561</t>
+          <t>269669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545234</t>
+          <t>545369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>603966</t>
+          <t>605474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114634</t>
+          <t>115647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154095</t>
+          <t>155849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53171</t>
+          <t>52988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81100</t>
+          <t>81094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176837</t>
+          <t>173255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>226097</t>
+          <t>224130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274202</t>
+          <t>272448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313663</t>
+          <t>312650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212563</t>
+          <t>212569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240492</t>
+          <t>240675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>495862</t>
+          <t>497829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>545122</t>
+          <t>548704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126893</t>
+          <t>127685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168044</t>
+          <t>167577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78041</t>
+          <t>79495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111330</t>
+          <t>113077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>216303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270505</t>
+          <t>269446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273579</t>
+          <t>274046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314730</t>
+          <t>313938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256718</t>
+          <t>254971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290007</t>
+          <t>288553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>539166</t>
+          <t>540225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>592828</t>
+          <t>593368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>598347</t>
+          <t>596422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>681670</t>
+          <t>678993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>291263</t>
+          <t>295955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>356031</t>
+          <t>357459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>904954</t>
+          <t>908851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1013420</t>
+          <t>1015207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1087169</t>
+          <t>1089846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1170492</t>
+          <t>1172417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>888469</t>
+          <t>887041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>953237</t>
+          <t>948545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1999919</t>
+          <t>1998132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2108385</t>
+          <t>2104488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>110328</t>
+          <t>116540</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94013</t>
+          <t>97895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129998</t>
+          <t>133710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21973</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>41293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>140297</t>
+          <t>146864</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121852</t>
+          <t>128088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161168</t>
+          <t>166788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>179613</t>
+          <t>195888</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159943</t>
+          <t>178718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>195928</t>
+          <t>214533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138915</t>
+          <t>149499</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129170</t>
+          <t>138530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146911</t>
+          <t>157959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>318528</t>
+          <t>345387</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>297657</t>
+          <t>325463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>336973</t>
+          <t>364163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,98%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>312428</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>179823</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>179823</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>179823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>458825</t>
+          <t>492251</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>458825</t>
+          <t>492251</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>458825</t>
+          <t>492251</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>120616</t>
+          <t>126822</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>108532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>206751</t>
+          <t>148008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56117</t>
+          <t>61208</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>49747</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68823</t>
+          <t>76066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>176733</t>
+          <t>188030</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81419</t>
+          <t>167044</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>254213</t>
+          <t>216529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>512327</t>
+          <t>294908</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426192</t>
+          <t>273722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590764</t>
+          <t>313198</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>203597</t>
+          <t>220840</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190891</t>
+          <t>205982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>214248</t>
+          <t>232301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>715924</t>
+          <t>515748</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>638444</t>
+          <t>487249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>811238</t>
+          <t>536734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>632943</t>
+          <t>421730</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>632943</t>
+          <t>421730</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>632943</t>
+          <t>421730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>259714</t>
+          <t>282048</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>259714</t>
+          <t>282048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>259714</t>
+          <t>282048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>892657</t>
+          <t>703778</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>892657</t>
+          <t>703778</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>892657</t>
+          <t>703778</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>117424</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88927</t>
+          <t>96563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129937</t>
+          <t>137243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>67199</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50784</t>
+          <t>54795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76251</t>
+          <t>82437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>171391</t>
+          <t>184624</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148200</t>
+          <t>162004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201225</t>
+          <t>211375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>231989</t>
+          <t>259316</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210355</t>
+          <t>239497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>251365</t>
+          <t>280177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>164472</t>
+          <t>186507</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151308</t>
+          <t>171269</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176775</t>
+          <t>198911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>396461</t>
+          <t>445822</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>366627</t>
+          <t>419071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>419652</t>
+          <t>468442</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>340292</t>
+          <t>376740</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>340292</t>
+          <t>376740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>340292</t>
+          <t>376740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>227559</t>
+          <t>253706</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>227559</t>
+          <t>253706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>227559</t>
+          <t>253706</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>567852</t>
+          <t>630446</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>567852</t>
+          <t>630446</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>567852</t>
+          <t>630446</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>148721</t>
+          <t>158217</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129964</t>
+          <t>138060</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169236</t>
+          <t>177271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85887</t>
+          <t>89132</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73284</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99119</t>
+          <t>104453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>234609</t>
+          <t>247349</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>221454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>258860</t>
+          <t>271979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>257722</t>
+          <t>277339</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237207</t>
+          <t>258285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276479</t>
+          <t>297496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>231667</t>
+          <t>251205</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218435</t>
+          <t>235884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>244270</t>
+          <t>264335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>489388</t>
+          <t>528544</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>465137</t>
+          <t>503914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>512279</t>
+          <t>554439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>406443</t>
+          <t>435556</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>406443</t>
+          <t>435556</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>406443</t>
+          <t>435556</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>317554</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>317554</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>317554</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>723997</t>
+          <t>775893</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>723997</t>
+          <t>775893</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>723997</t>
+          <t>775893</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>487969</t>
+          <t>519004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>296898</t>
+          <t>480345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>587979</t>
+          <t>557676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>247863</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210736</t>
+          <t>223224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259962</t>
+          <t>273858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>723029</t>
+          <t>766867</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>509845</t>
+          <t>720426</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>811062</t>
+          <t>809577</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1181651</t>
+          <t>1027450</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1081641</t>
+          <t>988778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1372722</t>
+          <t>1066109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>738651</t>
+          <t>808051</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>713749</t>
+          <t>782056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>762975</t>
+          <t>832690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1920302</t>
+          <t>1835501</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1832269</t>
+          <t>1792791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2133486</t>
+          <t>1881942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1669620</t>
+          <t>1546454</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>973711</t>
+          <t>1055914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2643331</t>
+          <t>2602368</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
